--- a/NUMEX_pre_RStudio/models_iWUE.xlsx
+++ b/NUMEX_pre_RStudio/models_iWUE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -107,196 +107,247 @@
     <t xml:space="preserve">iWUE | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">85.255***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.760)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.543*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.897)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.632)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.335)</t>
+    <t xml:space="preserve">25.326***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.783)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.616*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.932)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.671)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.372)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.865</t>
   </si>
   <si>
     <t xml:space="preserve">36</t>
   </si>
   <si>
-    <t xml:space="preserve">306.6</t>
+    <t xml:space="preserve">0.152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.4</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">96.605***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.793)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.586)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.663)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.652</t>
+    <t xml:space="preserve">36.734***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.822)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.644)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.702)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5</t>
+    <t xml:space="preserve">0.353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.5</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">146.941***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.486)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.654)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.093)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.019)</t>
+    <t xml:space="preserve">87.340***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.521)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.154)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.542)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.556)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.229</t>
   </si>
   <si>
     <t xml:space="preserve">45</t>
   </si>
   <si>
-    <t xml:space="preserve">380.4</t>
+    <t xml:space="preserve">0.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.6</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">131.326***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.817)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.471)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.570)</t>
+    <t xml:space="preserve">71.629***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.841)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.494)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.593)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.859</t>
   </si>
   <si>
     <t xml:space="preserve">50</t>
   </si>
   <si>
-    <t xml:space="preserve">394.5</t>
+    <t xml:space="preserve">0.057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380.1</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">143.373***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.140)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.376)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(14.926)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.968)</t>
+    <t xml:space="preserve">83.737***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.186)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12.438)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(15.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.541</t>
   </si>
   <si>
     <t xml:space="preserve">21</t>
   </si>
   <si>
-    <t xml:space="preserve">191.9</t>
+    <t xml:space="preserve">0.188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.5</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">132.488***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.734)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.694)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.264+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.856)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.409)</t>
+    <t xml:space="preserve">72.502***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.986)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.516)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.676)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.247)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.237</t>
   </si>
   <si>
     <t xml:space="preserve">18</t>
   </si>
   <si>
-    <t xml:space="preserve">141.5</t>
+    <t xml:space="preserve">0.155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.5</t>
   </si>
   <si>
     <t xml:space="preserve">d13C | 1000 | Pouteria</t>
@@ -326,9 +377,6 @@
     <t xml:space="preserve">(0.446)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.960</t>
   </si>
   <si>
@@ -404,9 +452,6 @@
     <t xml:space="preserve">1.161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.039</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.240</t>
   </si>
   <si>
@@ -443,9 +488,6 @@
     <t xml:space="preserve">0.966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.057</t>
-  </si>
-  <si>
     <t xml:space="preserve">149.5</t>
   </si>
   <si>
@@ -479,9 +521,6 @@
     <t xml:space="preserve">1.677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188</t>
-  </si>
-  <si>
     <t xml:space="preserve">84.3</t>
   </si>
   <si>
@@ -521,223 +560,208 @@
     <t xml:space="preserve">0.154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236</t>
-  </si>
-  <si>
     <t xml:space="preserve">53.3</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">286.706***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.615)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-23.269*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.035)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.212)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.736)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.2</t>
+    <t xml:space="preserve">382.592***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.654)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-23.386*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12.273)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.795)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.5</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">268.546***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(18.537)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.261)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-15.444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0</t>
+    <t xml:space="preserve">364.340***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.315)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(18.630)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12.323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-15.521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">187.980***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.789)</t>
+    <t xml:space="preserve">283.370***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.834)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.106</t>
   </si>
   <si>
-    <t xml:space="preserve">(9.797)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.414)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.845)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.8</t>
+    <t xml:space="preserve">(9.846)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.467)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.889)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.2</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">212.993***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.875)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.708)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.154)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">422.9</t>
+    <t xml:space="preserve">308.509***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.746)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.190)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.349)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423.4</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">193.717***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(14.625)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(19.802)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-38.076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(23.882)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(19.148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.3</t>
+    <t xml:space="preserve">289.135***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(14.698)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(19.901)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-38.268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(24.002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(19.244)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.4</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">211.602***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.938)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.373)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13.812)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.946)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.5</t>
+    <t xml:space="preserve">307.110***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.425)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13.881)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.996)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.6</t>
   </si>
 </sst>
 </file>
@@ -1260,821 +1284,821 @@
         <v>38</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
       </c>
       <c r="O4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="L5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M5" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="L6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M6" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="N6" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="O6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="L7" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="M7" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="N8" t="s">
         <v>29</v>
       </c>
       <c r="O8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="L9" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="M9" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="N9" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="O9" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="H10" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I10" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="J10" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K10" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="L10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="G11" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="H11" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I11" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J11" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K11" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="L11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M11" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
       </c>
       <c r="O11" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="F12" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="H12" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="I12" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="J12" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="K12" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M12" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="N12" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="O12" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="I13" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="J13" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K13" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="M13" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
       </c>
       <c r="O13" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="F14" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G14" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="H14" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="I14" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="J14" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K14" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="M14" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
       </c>
       <c r="O14" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="G15" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="H15" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="I15" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="J15" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="K15" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="L15" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="M15" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="O15" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D16" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F16" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="G16" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="H16" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="I16" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K16" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M16" t="s">
-        <v>181</v>
+        <v>42</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
       </c>
       <c r="O16" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F17" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="G17" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="H17" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="I17" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="J17" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K17" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="L17" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M17" t="s">
-        <v>192</v>
+        <v>54</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
       </c>
       <c r="O17" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D18" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="F18" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="G18" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H18" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I18" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="J18" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="K18" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M18" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="N18" t="s">
-        <v>205</v>
+        <v>69</v>
       </c>
       <c r="O18" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C19" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D19" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E19" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F19" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G19" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="H19" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I19" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="J19" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K19" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="M19" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
       </c>
       <c r="O19" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E20" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F20" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="G20" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="H20" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="I20" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="J20" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K20" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="M20" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
       </c>
       <c r="O20" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D21" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G21" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H21" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="I21" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="J21" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="K21" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="L21" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="M21" t="s">
-        <v>240</v>
+        <v>109</v>
       </c>
       <c r="N21" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="O21" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/NUMEX_pre_RStudio/models_iWUE.xlsx
+++ b/NUMEX_pre_RStudio/models_iWUE.xlsx
@@ -350,7 +350,7 @@
     <t xml:space="preserve">123.5</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 1000 | Pouteria</t>
+    <t xml:space="preserve">δ13C | 1000 | Pouteria</t>
   </si>
   <si>
     <t xml:space="preserve">-31.553***</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">108.9</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 1000 | Clarisia</t>
+    <t xml:space="preserve">δ13C | 1000 | Clarisia</t>
   </si>
   <si>
     <t xml:space="preserve">-30.630***</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">35.4</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 2000 | Alchornea</t>
+    <t xml:space="preserve">δ13C | 2000 | Alchornea</t>
   </si>
   <si>
     <t xml:space="preserve">-26.513***</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">154.2</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 2000 | Myrcia</t>
+    <t xml:space="preserve">δ13C | 2000 | Myrcia</t>
   </si>
   <si>
     <t xml:space="preserve">-27.794***</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">149.5</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 3000 | Hedyosmum</t>
+    <t xml:space="preserve">δ13C | 3000 | Hedyosmum</t>
   </si>
   <si>
     <t xml:space="preserve">-26.806***</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">84.3</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 3000 | Weinmannia</t>
+    <t xml:space="preserve">δ13C | 3000 | Weinmannia</t>
   </si>
   <si>
     <t xml:space="preserve">-27.724***</t>

--- a/NUMEX_pre_RStudio/models_iWUE.xlsx
+++ b/NUMEX_pre_RStudio/models_iWUE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -107,34 +107,34 @@
     <t xml:space="preserve">iWUE | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">25.326***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.783)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.616*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.932)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.671)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.372)</t>
+    <t xml:space="preserve">25.624***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.760)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.546*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.634)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.336)</t>
   </si>
   <si>
     <t xml:space="preserve">0.000</t>
   </si>
   <si>
-    <t xml:space="preserve">15.865</t>
+    <t xml:space="preserve">15.789</t>
   </si>
   <si>
     <t xml:space="preserve">36</t>
@@ -143,34 +143,34 @@
     <t xml:space="preserve">0.152</t>
   </si>
   <si>
-    <t xml:space="preserve">288.4</t>
+    <t xml:space="preserve">288.1</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">36.734***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.822)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.644)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.702)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084</t>
+    <t xml:space="preserve">36.976***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.794)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.588)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.665)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.035</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>
@@ -185,34 +185,34 @@
     <t xml:space="preserve">iWUE | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">87.340***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.521)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.154)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.542)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.556)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.229</t>
+    <t xml:space="preserve">87.624***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.465)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.485)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.507)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.106</t>
   </si>
   <si>
     <t xml:space="preserve">45</t>
@@ -221,40 +221,40 @@
     <t xml:space="preserve">0.039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.6</t>
+    <t xml:space="preserve">0.240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.9</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">71.629***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.062)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.841)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.494)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.593)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.859</t>
+    <t xml:space="preserve">72.017***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.032)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.794)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.450)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.548)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.743</t>
   </si>
   <si>
     <t xml:space="preserve">50</t>
@@ -263,37 +263,37 @@
     <t xml:space="preserve">0.057</t>
   </si>
   <si>
-    <t xml:space="preserve">380.1</t>
+    <t xml:space="preserve">379.2</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">83.737***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.186)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.438)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(15.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.028)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.541</t>
+    <t xml:space="preserve">83.754***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.142)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12.379)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(14.929)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.970)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.443</t>
   </si>
   <si>
     <t xml:space="preserve">21</t>
@@ -302,40 +302,37 @@
     <t xml:space="preserve">0.188</t>
   </si>
   <si>
-    <t xml:space="preserve">169.5</t>
+    <t xml:space="preserve">169.3</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">72.502***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.986)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.516)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.676)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.247)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.237</t>
+    <t xml:space="preserve">72.573***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.962)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.634)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.217)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.188</t>
   </si>
   <si>
     <t xml:space="preserve">18</t>
@@ -347,10 +344,10 @@
     <t xml:space="preserve">0.236</t>
   </si>
   <si>
-    <t xml:space="preserve">123.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">δ13C | 1000 | Pouteria</t>
+    <t xml:space="preserve">123.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 1000 | Pouteria</t>
   </si>
   <si>
     <t xml:space="preserve">-31.553***</t>
@@ -386,7 +383,7 @@
     <t xml:space="preserve">108.9</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 1000 | Clarisia</t>
+    <t xml:space="preserve">d13C | 1000 | Clarisia</t>
   </si>
   <si>
     <t xml:space="preserve">-30.630***</t>
@@ -419,7 +416,7 @@
     <t xml:space="preserve">35.4</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 2000 | Alchornea</t>
+    <t xml:space="preserve">d13C | 2000 | Alchornea</t>
   </si>
   <si>
     <t xml:space="preserve">-26.513***</t>
@@ -452,13 +449,10 @@
     <t xml:space="preserve">1.161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.240</t>
-  </si>
-  <si>
     <t xml:space="preserve">154.2</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 2000 | Myrcia</t>
+    <t xml:space="preserve">d13C | 2000 | Myrcia</t>
   </si>
   <si>
     <t xml:space="preserve">-27.794***</t>
@@ -491,7 +485,7 @@
     <t xml:space="preserve">149.5</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 3000 | Hedyosmum</t>
+    <t xml:space="preserve">d13C | 3000 | Hedyosmum</t>
   </si>
   <si>
     <t xml:space="preserve">-26.806***</t>
@@ -524,7 +518,7 @@
     <t xml:space="preserve">84.3</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 3000 | Weinmannia</t>
+    <t xml:space="preserve">d13C | 3000 | Weinmannia</t>
   </si>
   <si>
     <t xml:space="preserve">-27.724***</t>
@@ -566,202 +560,181 @@
     <t xml:space="preserve">Ci | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">382.592***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.654)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-23.386*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.091)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.273)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.795)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.5</t>
+    <t xml:space="preserve">0.903***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.055*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.029)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-68.5</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">364.340***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.315)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(18.630)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-15.521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1</t>
+    <t xml:space="preserve">0.860***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.044)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.7</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">283.370***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.834)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.846)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.467)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.889)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.2</t>
+    <t xml:space="preserve">0.666***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-97.7</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">308.509***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.746)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.190)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.349)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">423.4</t>
+    <t xml:space="preserve">0.725***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-133.3</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">289.135***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(14.698)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(19.901)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-38.268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(24.002)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(19.244)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.4</t>
+    <t xml:space="preserve">0.682***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.057)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.045)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.2</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">307.110***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.425)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13.881)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.996)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.6</t>
+    <t xml:space="preserve">0.724***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.033)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-32.7</t>
   </si>
 </sst>
 </file>
@@ -1504,166 +1477,166 @@
         <v>100</v>
       </c>
       <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
         <v>101</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>102</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>103</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>104</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>105</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>106</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>107</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>108</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>109</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>110</v>
-      </c>
-      <c r="O9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" t="s">
         <v>112</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>113</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>114</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>115</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>116</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>117</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>118</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>119</v>
-      </c>
-      <c r="I10" t="s">
-        <v>120</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
       </c>
       <c r="K10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L10" t="s">
         <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" t="s">
         <v>124</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>125</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>126</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>127</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>128</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>129</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>130</v>
       </c>
-      <c r="H11" t="s">
-        <v>131</v>
-      </c>
       <c r="I11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J11" t="s">
         <v>39</v>
       </c>
       <c r="K11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s">
         <v>53</v>
       </c>
       <c r="M11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
       </c>
       <c r="O11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" t="s">
         <v>135</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>136</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>137</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>138</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>139</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>140</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>141</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>142</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>143</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>144</v>
-      </c>
-      <c r="K12" t="s">
-        <v>145</v>
       </c>
       <c r="L12" t="s">
         <v>67</v>
@@ -1672,45 +1645,45 @@
         <v>68</v>
       </c>
       <c r="N12" t="s">
-        <v>146</v>
+        <v>69</v>
       </c>
       <c r="O12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" t="s">
         <v>148</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>149</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>150</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>151</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>152</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>153</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>154</v>
-      </c>
-      <c r="H13" t="s">
-        <v>155</v>
-      </c>
-      <c r="I13" t="s">
-        <v>156</v>
       </c>
       <c r="J13" t="s">
         <v>39</v>
       </c>
       <c r="K13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s">
         <v>81</v>
@@ -1722,42 +1695,42 @@
         <v>29</v>
       </c>
       <c r="O13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" t="s">
         <v>159</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>160</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>161</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>162</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>163</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>164</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>165</v>
-      </c>
-      <c r="H14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I14" t="s">
-        <v>167</v>
       </c>
       <c r="J14" t="s">
         <v>39</v>
       </c>
       <c r="K14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s">
         <v>94</v>
@@ -1769,89 +1742,89 @@
         <v>29</v>
       </c>
       <c r="O14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" t="s">
         <v>170</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>171</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>172</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>173</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>174</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>175</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>176</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>177</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>178</v>
       </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
+        <v>107</v>
+      </c>
+      <c r="M15" t="s">
         <v>179</v>
       </c>
-      <c r="K15" t="s">
+      <c r="N15" t="s">
+        <v>109</v>
+      </c>
+      <c r="O15" t="s">
         <v>180</v>
-      </c>
-      <c r="L15" t="s">
-        <v>108</v>
-      </c>
-      <c r="M15" t="s">
-        <v>181</v>
-      </c>
-      <c r="N15" t="s">
-        <v>110</v>
-      </c>
-      <c r="O15" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" t="s">
         <v>183</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>184</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>185</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>186</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>187</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>188</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>189</v>
-      </c>
-      <c r="H16" t="s">
-        <v>190</v>
-      </c>
-      <c r="I16" t="s">
-        <v>191</v>
       </c>
       <c r="J16" t="s">
         <v>39</v>
       </c>
       <c r="K16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s">
         <v>41</v>
@@ -1863,42 +1836,42 @@
         <v>29</v>
       </c>
       <c r="O16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" t="s">
         <v>194</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>195</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>196</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>197</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" t="s">
         <v>198</v>
       </c>
-      <c r="F17" t="s">
-        <v>199</v>
-      </c>
-      <c r="G17" t="s">
-        <v>200</v>
-      </c>
-      <c r="H17" t="s">
-        <v>201</v>
-      </c>
       <c r="I17" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
       </c>
       <c r="K17" t="s">
-        <v>202</v>
+        <v>121</v>
       </c>
       <c r="L17" t="s">
         <v>53</v>
@@ -1910,42 +1883,42 @@
         <v>29</v>
       </c>
       <c r="O17" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F18" t="s">
         <v>204</v>
       </c>
-      <c r="B18" t="s">
+      <c r="G18" t="s">
         <v>205</v>
       </c>
-      <c r="C18" t="s">
+      <c r="H18" t="s">
         <v>206</v>
       </c>
-      <c r="D18" t="s">
+      <c r="I18" t="s">
+        <v>202</v>
+      </c>
+      <c r="J18" t="s">
         <v>207</v>
       </c>
-      <c r="E18" t="s">
+      <c r="K18" t="s">
         <v>208</v>
-      </c>
-      <c r="F18" t="s">
-        <v>209</v>
-      </c>
-      <c r="G18" t="s">
-        <v>210</v>
-      </c>
-      <c r="H18" t="s">
-        <v>211</v>
-      </c>
-      <c r="I18" t="s">
-        <v>212</v>
-      </c>
-      <c r="J18" t="s">
-        <v>213</v>
-      </c>
-      <c r="K18" t="s">
-        <v>214</v>
       </c>
       <c r="L18" t="s">
         <v>67</v>
@@ -1954,45 +1927,45 @@
         <v>68</v>
       </c>
       <c r="N18" t="s">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="O18" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F19" t="s">
+        <v>215</v>
+      </c>
+      <c r="G19" t="s">
         <v>216</v>
       </c>
-      <c r="B19" t="s">
+      <c r="H19" t="s">
         <v>217</v>
       </c>
-      <c r="C19" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" t="s">
-        <v>219</v>
-      </c>
-      <c r="E19" t="s">
-        <v>220</v>
-      </c>
-      <c r="F19" t="s">
-        <v>221</v>
-      </c>
-      <c r="G19" t="s">
-        <v>222</v>
-      </c>
-      <c r="H19" t="s">
-        <v>223</v>
-      </c>
       <c r="I19" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="J19" t="s">
         <v>39</v>
       </c>
       <c r="K19" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s">
         <v>81</v>
@@ -2004,42 +1977,42 @@
         <v>29</v>
       </c>
       <c r="O19" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" t="s">
+        <v>221</v>
+      </c>
+      <c r="C20" t="s">
+        <v>222</v>
+      </c>
+      <c r="D20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E20" t="s">
+        <v>224</v>
+      </c>
+      <c r="F20" t="s">
+        <v>225</v>
+      </c>
+      <c r="G20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H20" t="s">
         <v>227</v>
       </c>
-      <c r="B20" t="s">
+      <c r="I20" t="s">
         <v>228</v>
-      </c>
-      <c r="C20" t="s">
-        <v>229</v>
-      </c>
-      <c r="D20" t="s">
-        <v>230</v>
-      </c>
-      <c r="E20" t="s">
-        <v>231</v>
-      </c>
-      <c r="F20" t="s">
-        <v>232</v>
-      </c>
-      <c r="G20" t="s">
-        <v>233</v>
-      </c>
-      <c r="H20" t="s">
-        <v>234</v>
-      </c>
-      <c r="I20" t="s">
-        <v>235</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
       </c>
       <c r="K20" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s">
         <v>94</v>
@@ -2051,54 +2024,54 @@
         <v>29</v>
       </c>
       <c r="O20" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" t="s">
+        <v>233</v>
+      </c>
+      <c r="D21" t="s">
+        <v>234</v>
+      </c>
+      <c r="E21" t="s">
+        <v>205</v>
+      </c>
+      <c r="F21" t="s">
+        <v>235</v>
+      </c>
+      <c r="G21" t="s">
+        <v>236</v>
+      </c>
+      <c r="H21" t="s">
+        <v>237</v>
+      </c>
+      <c r="I21" t="s">
         <v>238</v>
       </c>
-      <c r="B21" t="s">
+      <c r="J21" t="s">
         <v>239</v>
       </c>
-      <c r="C21" t="s">
+      <c r="K21" t="s">
+        <v>68</v>
+      </c>
+      <c r="L21" t="s">
+        <v>107</v>
+      </c>
+      <c r="M21" t="s">
+        <v>108</v>
+      </c>
+      <c r="N21" t="s">
+        <v>109</v>
+      </c>
+      <c r="O21" t="s">
         <v>240</v>
-      </c>
-      <c r="D21" t="s">
-        <v>241</v>
-      </c>
-      <c r="E21" t="s">
-        <v>242</v>
-      </c>
-      <c r="F21" t="s">
-        <v>243</v>
-      </c>
-      <c r="G21" t="s">
-        <v>244</v>
-      </c>
-      <c r="H21" t="s">
-        <v>245</v>
-      </c>
-      <c r="I21" t="s">
-        <v>246</v>
-      </c>
-      <c r="J21" t="s">
-        <v>247</v>
-      </c>
-      <c r="K21" t="s">
-        <v>248</v>
-      </c>
-      <c r="L21" t="s">
-        <v>108</v>
-      </c>
-      <c r="M21" t="s">
-        <v>109</v>
-      </c>
-      <c r="N21" t="s">
-        <v>110</v>
-      </c>
-      <c r="O21" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/NUMEX_pre_RStudio/models_iWUE.xlsx
+++ b/NUMEX_pre_RStudio/models_iWUE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">(Intercept)</t>
   </si>
   <si>
-    <t xml:space="preserve">SUBN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBP</t>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N × P</t>
   </si>
   <si>
     <t xml:space="preserve">SD (Intercept Bloque)</t>
@@ -119,18 +119,18 @@
     <t xml:space="preserve">(6.899)</t>
   </si>
   <si>
-    <t xml:space="preserve">-2.266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.634)</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.507</t>
   </si>
   <si>
     <t xml:space="preserve">(7.336)</t>
   </si>
   <si>
+    <t xml:space="preserve">-20.319+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.694)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.000</t>
   </si>
   <si>
@@ -161,13 +161,16 @@
     <t xml:space="preserve">(11.588)</t>
   </si>
   <si>
-    <t xml:space="preserve">-3.011</t>
+    <t xml:space="preserve">9.654</t>
   </si>
   <si>
     <t xml:space="preserve">(7.665)</t>
   </si>
   <si>
-    <t xml:space="preserve">9.654</t>
+    <t xml:space="preserve">1.726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13.588)</t>
   </si>
   <si>
     <t xml:space="preserve">10.035</t>
@@ -197,138 +200,141 @@
     <t xml:space="preserve">(6.100)</t>
   </si>
   <si>
-    <t xml:space="preserve">-3.023</t>
+    <t xml:space="preserve">-7.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.507)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.734)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.017***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.032)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.794)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.548)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.714)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">379.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.754***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.142)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12.379)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.970)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(18.768)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.573***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.962)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.231</t>
   </si>
   <si>
     <t xml:space="preserve">(6.485)</t>
   </si>
   <si>
-    <t xml:space="preserve">-7.081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.507)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.017***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.032)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.794)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.450)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.548)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">379.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.754***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.142)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.379)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(14.929)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.970)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.573***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.962)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.634)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-7.506</t>
   </si>
   <si>
     <t xml:space="preserve">(6.217)</t>
   </si>
   <si>
+    <t xml:space="preserve">-3.086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.545)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.322</t>
   </si>
   <si>
@@ -347,7 +353,7 @@
     <t xml:space="preserve">123.4</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 1000 | Pouteria</t>
+    <t xml:space="preserve">δ13C | 1000 | Pouteria</t>
   </si>
   <si>
     <t xml:space="preserve">-31.553***</t>
@@ -362,18 +368,18 @@
     <t xml:space="preserve">(0.419)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.464)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.285</t>
   </si>
   <si>
     <t xml:space="preserve">(0.446)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.650)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.960</t>
   </si>
   <si>
@@ -383,7 +389,7 @@
     <t xml:space="preserve">108.9</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 1000 | Clarisia</t>
+    <t xml:space="preserve">δ13C | 1000 | Clarisia</t>
   </si>
   <si>
     <t xml:space="preserve">-30.630***</t>
@@ -398,13 +404,16 @@
     <t xml:space="preserve">(0.945)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.245</t>
+    <t xml:space="preserve">0.788</t>
   </si>
   <si>
     <t xml:space="preserve">(0.625)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788</t>
+    <t xml:space="preserve">0.138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.108)</t>
   </si>
   <si>
     <t xml:space="preserve">0.818</t>
@@ -416,7 +425,7 @@
     <t xml:space="preserve">35.4</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 2000 | Alchornea</t>
+    <t xml:space="preserve">δ13C | 2000 | Alchornea</t>
   </si>
   <si>
     <t xml:space="preserve">-26.513***</t>
@@ -431,18 +440,18 @@
     <t xml:space="preserve">(0.502)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.534)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.581</t>
   </si>
   <si>
     <t xml:space="preserve">(0.453)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.719)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.598</t>
   </si>
   <si>
@@ -452,7 +461,7 @@
     <t xml:space="preserve">154.2</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 2000 | Myrcia</t>
+    <t xml:space="preserve">δ13C | 2000 | Myrcia</t>
   </si>
   <si>
     <t xml:space="preserve">-27.794***</t>
@@ -467,25 +476,25 @@
     <t xml:space="preserve">(0.395)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.366)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.457</t>
   </si>
   <si>
     <t xml:space="preserve">(0.374)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.553)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.966</t>
   </si>
   <si>
     <t xml:space="preserve">149.5</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 3000 | Hedyosmum</t>
+    <t xml:space="preserve">δ13C | 3000 | Hedyosmum</t>
   </si>
   <si>
     <t xml:space="preserve">-26.806***</t>
@@ -500,25 +509,25 @@
     <t xml:space="preserve">(1.016)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.225)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.483</t>
   </si>
   <si>
     <t xml:space="preserve">(0.982)</t>
   </si>
   <si>
+    <t xml:space="preserve">1.986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.540)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.677</t>
   </si>
   <si>
     <t xml:space="preserve">84.3</t>
   </si>
   <si>
-    <t xml:space="preserve">d13C | 3000 | Weinmannia</t>
+    <t xml:space="preserve">δ13C | 3000 | Weinmannia</t>
   </si>
   <si>
     <t xml:space="preserve">-27.724***</t>
@@ -533,18 +542,18 @@
     <t xml:space="preserve">(0.531)</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.706)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.613</t>
   </si>
   <si>
     <t xml:space="preserve">(0.509)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.863)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.272</t>
   </si>
   <si>
@@ -572,43 +581,49 @@
     <t xml:space="preserve">(0.026)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.009</t>
+    <t xml:space="preserve">-0.013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.077+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-68.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ci | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.044)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.037</t>
   </si>
   <si>
     <t xml:space="preserve">(0.029)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.028)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-68.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ci | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.044)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.037</t>
+    <t xml:space="preserve">-0.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.052)</t>
   </si>
   <si>
     <t xml:space="preserve">-13.7</t>
@@ -626,109 +641,112 @@
     <t xml:space="preserve">(0.023)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.033)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-97.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ci | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-133.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ci | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.682***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.045)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.071)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ci | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.724***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.024)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.012</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-97.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ci | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.017)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-133.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ci | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.682***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.035)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.057)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.045)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-20.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ci | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.724***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.019)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.033)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.024)</t>
+    <t xml:space="preserve">(0.040)</t>
   </si>
   <si>
     <t xml:space="preserve">0.013</t>
@@ -1301,530 +1319,530 @@
         <v>51</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
         <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
       </c>
       <c r="O5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" t="s">
         <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
       </c>
       <c r="O7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J8" t="s">
         <v>39</v>
       </c>
       <c r="K8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N8" t="s">
         <v>29</v>
       </c>
       <c r="O8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
       </c>
       <c r="K10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L10" t="s">
         <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J11" t="s">
         <v>39</v>
       </c>
       <c r="K11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
       </c>
       <c r="O11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J12" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K12" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J13" t="s">
         <v>39</v>
       </c>
       <c r="K13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
       </c>
       <c r="O13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G14" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J14" t="s">
         <v>39</v>
       </c>
       <c r="K14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
       </c>
       <c r="O14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C16" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G16" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H16" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J16" t="s">
         <v>39</v>
       </c>
       <c r="K16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s">
         <v>41</v>
@@ -1836,242 +1854,242 @@
         <v>29</v>
       </c>
       <c r="O16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D17" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F17" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G17" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="H17" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I17" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
       </c>
       <c r="K17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
       </c>
       <c r="O17" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D18" t="s">
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F18" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="G18" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H18" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I18" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="J18" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K18" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="O18" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C19" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E19" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G19" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H19" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I19" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="J19" t="s">
         <v>39</v>
       </c>
       <c r="K19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
       </c>
       <c r="O19" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C20" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E20" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F20" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H20" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I20" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
       </c>
       <c r="K20" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
       </c>
       <c r="O20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C21" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D21" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E21" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="F21" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G21" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H21" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="I21" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="J21" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="K21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O21" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/NUMEX_pre_RStudio/models_iWUE.xlsx
+++ b/NUMEX_pre_RStudio/models_iWUE.xlsx
@@ -353,7 +353,7 @@
     <t xml:space="preserve">123.4</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 1000 | Pouteria</t>
+    <t xml:space="preserve">d13C | 1000 | Pouteria</t>
   </si>
   <si>
     <t xml:space="preserve">-31.553***</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">108.9</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 1000 | Clarisia</t>
+    <t xml:space="preserve">d13C | 1000 | Clarisia</t>
   </si>
   <si>
     <t xml:space="preserve">-30.630***</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">35.4</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 2000 | Alchornea</t>
+    <t xml:space="preserve">d13C | 2000 | Alchornea</t>
   </si>
   <si>
     <t xml:space="preserve">-26.513***</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">154.2</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 2000 | Myrcia</t>
+    <t xml:space="preserve">d13C | 2000 | Myrcia</t>
   </si>
   <si>
     <t xml:space="preserve">-27.794***</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">149.5</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 3000 | Hedyosmum</t>
+    <t xml:space="preserve">d13C | 3000 | Hedyosmum</t>
   </si>
   <si>
     <t xml:space="preserve">-26.806***</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">84.3</t>
   </si>
   <si>
-    <t xml:space="preserve">δ13C | 3000 | Weinmannia</t>
+    <t xml:space="preserve">d13C | 3000 | Weinmannia</t>
   </si>
   <si>
     <t xml:space="preserve">-27.724***</t>

--- a/NUMEX_pre_RStudio/models_iWUE.xlsx
+++ b/NUMEX_pre_RStudio/models_iWUE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -35,18 +35,6 @@
     <t xml:space="preserve">estimates.5</t>
   </si>
   <si>
-    <t xml:space="preserve">estimates.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">gof</t>
   </si>
   <si>
@@ -98,43 +86,28 @@
     <t xml:space="preserve">estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">std.error</t>
-  </si>
-  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">25.624***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.760)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.546*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.336)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-20.319+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.694)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.789</t>
+    <t xml:space="preserve">25.624*** (SE = 4.760, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.546* (SE = 6.899, p = 0.043)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.507 (SE = 7.336, p = 0.636)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.319+ (SE = 10.694, p = 0.067)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.789 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">36</t>
@@ -149,31 +122,19 @@
     <t xml:space="preserve">iWUE | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">36.976***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.794)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.588)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.665)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13.588)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.035</t>
+    <t xml:space="preserve">36.976*** (SE = 5.794, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.390 (SE = 11.588, p = 0.261)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.654 (SE = 7.665, p = 0.255)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.726 (SE = 13.588, p = 0.903)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.035 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>
@@ -188,34 +149,22 @@
     <t xml:space="preserve">iWUE | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">87.624***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.465)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.507)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.734)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.106</t>
+    <t xml:space="preserve">87.624*** (SE = 5.465, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036 (SE = 6.100, p = 0.995)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.081 (SE = 5.507, p = 0.206)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.022 (SE = 8.734, p = 0.648)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.244 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.106 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">45</t>
@@ -233,31 +182,19 @@
     <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">72.017***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.032)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.794)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.548)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.714)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.743</t>
+    <t xml:space="preserve">72.017*** (SE = 3.032, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.687 (SE = 4.794, p = 0.170)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.608 (SE = 4.548, p = 0.224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.984 (SE = 6.714, p = 0.378)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.743 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">50</t>
@@ -272,31 +209,19 @@
     <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">83.754***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.142)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.379)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.970)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(18.768)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.443</t>
+    <t xml:space="preserve">83.754*** (SE = 9.142, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.492 (SE = 12.379, p = 0.664)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.891 (SE = 11.970, p = 0.630)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.202 (SE = 18.768, p = 0.217)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.443 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">21</t>
@@ -311,34 +236,22 @@
     <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">72.573***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.962)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.485)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.217)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.545)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188</t>
+    <t xml:space="preserve">72.573*** (SE = 4.962, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.231 (SE = 6.485, p = 0.526)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.506 (SE = 6.217, p = 0.251)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.086 (SE = 10.545, p = 0.775)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.322 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.188 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">18</t>
@@ -356,31 +269,19 @@
     <t xml:space="preserve">d13C | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">-31.553***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.419)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.446)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.650)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960</t>
+    <t xml:space="preserve">-31.553*** (SE = 0.289, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282 (SE = 0.419, p = 0.506)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285 (SE = 0.446, p = 0.527)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.750 (SE = 0.650, p = 0.258)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.038</t>
@@ -392,31 +293,19 @@
     <t xml:space="preserve">d13C | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">-30.630***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.472)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.945)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.625)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.108)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818</t>
+    <t xml:space="preserve">-30.630*** (SE = 0.472, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.170 (SE = 0.945, p = 0.262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788 (SE = 0.625, p = 0.254)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138 (SE = 1.108, p = 0.905)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.352</t>
@@ -428,34 +317,22 @@
     <t xml:space="preserve">d13C | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">-26.513***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.451)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.502)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.453)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.719)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.161</t>
+    <t xml:space="preserve">-26.513*** (SE = 0.451, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006 (SE = 0.502, p = 0.991)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.581 (SE = 0.453, p = 0.207)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332 (SE = 0.719, p = 0.647)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.161 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">154.2</t>
@@ -464,31 +341,19 @@
     <t xml:space="preserve">d13C | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">-27.794***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.250)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.395)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.374)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.553)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966</t>
+    <t xml:space="preserve">-27.794*** (SE = 0.250, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551 (SE = 0.395, p = 0.170)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457 (SE = 0.374, p = 0.228)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.486 (SE = 0.553, p = 0.384)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">149.5</t>
@@ -497,31 +362,19 @@
     <t xml:space="preserve">d13C | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">-26.806***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.750)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.016)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.982)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.540)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.677</t>
+    <t xml:space="preserve">-26.806*** (SE = 0.750, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453 (SE = 1.016, p = 0.662)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.483 (SE = 0.982, p = 0.630)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.986 (SE = 1.540, p = 0.217)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.677 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">84.3</t>
@@ -530,34 +383,22 @@
     <t xml:space="preserve">d13C | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">-27.724***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.406)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.531)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.509)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.863)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834</t>
+    <t xml:space="preserve">-27.724*** (SE = 0.406, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.346 (SE = 0.531, p = 0.527)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.613 (SE = 0.509, p = 0.251)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.253 (SE = 0.863, p = 0.775)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.154</t>
@@ -569,31 +410,19 @@
     <t xml:space="preserve">Ci | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.018)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.055*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.028)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.077+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.041)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.060</t>
+    <t xml:space="preserve">0.903*** (SE = 0.018, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.055* (SE = 0.026, p = 0.043)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.013 (SE = 0.028, p = 0.636)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.077+ (SE = 0.041, p = 0.067)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">-68.5</t>
@@ -602,28 +431,19 @@
     <t xml:space="preserve">Ci | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.044)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.029)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.052)</t>
+    <t xml:space="preserve">0.860*** (SE = 0.022, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055 (SE = 0.044, p = 0.261)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.037 (SE = 0.029, p = 0.255)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.007 (SE = 0.052, p = 0.903)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.038 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">-13.7</t>
@@ -632,28 +452,22 @@
     <t xml:space="preserve">Ci | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.033)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.054</t>
+    <t xml:space="preserve">0.666*** (SE = 0.021, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000 (SE = 0.023, p = 0.997)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.027 (SE = 0.021, p = 0.206)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.015 (SE = 0.033, p = 0.646)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.054 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.238</t>
@@ -665,25 +479,19 @@
     <t xml:space="preserve">Ci | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">0.725***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.017)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.045</t>
+    <t xml:space="preserve">0.725*** (SE = 0.012, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.025 (SE = 0.018, p = 0.171)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.022 (SE = 0.017, p = 0.219)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.023 (SE = 0.026, p = 0.373)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.045 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">-133.3</t>
@@ -692,31 +500,19 @@
     <t xml:space="preserve">Ci | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.035)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.045)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.071)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.078</t>
+    <t xml:space="preserve">0.682*** (SE = 0.035, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.021 (SE = 0.047, p = 0.664)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022 (SE = 0.045, p = 0.630)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.092 (SE = 0.071, p = 0.217)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.078 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">-20.2</t>
@@ -725,31 +521,22 @@
     <t xml:space="preserve">Ci | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.019)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.040)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.013</t>
+    <t xml:space="preserve">0.724*** (SE = 0.019, p = &lt;0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016 (SE = 0.025, p = 0.526)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029 (SE = 0.024, p = 0.251)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012 (SE = 0.040, p = 0.775)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.013 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.039 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">-32.7</t>
@@ -800,9 +587,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O21" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:O21"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K21" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K21"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="Modelo"/>
     <tableColumn id="2" name="estimates"/>
     <tableColumn id="3" name="estimates.1"/>
@@ -810,14 +597,10 @@
     <tableColumn id="5" name="estimates.3"/>
     <tableColumn id="6" name="estimates.4"/>
     <tableColumn id="7" name="estimates.5"/>
-    <tableColumn id="8" name="estimates.6"/>
-    <tableColumn id="9" name="estimates.7"/>
-    <tableColumn id="10" name="estimates.8"/>
-    <tableColumn id="11" name="estimates.9"/>
-    <tableColumn id="12" name="gof"/>
-    <tableColumn id="13" name="gof.1"/>
-    <tableColumn id="14" name="gof.2"/>
-    <tableColumn id="15" name="gof.3"/>
+    <tableColumn id="8" name="gof"/>
+    <tableColumn id="9" name="gof.1"/>
+    <tableColumn id="10" name="gof.2"/>
+    <tableColumn id="11" name="gof.3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1139,43 +922,31 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -1186,910 +957,670 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="G4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
+      <c r="I4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
         <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="I6" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
-      </c>
-      <c r="L6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" t="s">
-        <v>69</v>
-      </c>
-      <c r="N6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K7" t="s">
-        <v>81</v>
-      </c>
-      <c r="L7" t="s">
-        <v>82</v>
-      </c>
-      <c r="M7" t="s">
-        <v>83</v>
-      </c>
-      <c r="N7" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>94</v>
-      </c>
-      <c r="L8" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s">
-        <v>108</v>
-      </c>
-      <c r="L9" t="s">
-        <v>109</v>
-      </c>
-      <c r="M9" t="s">
-        <v>110</v>
-      </c>
-      <c r="N9" t="s">
-        <v>111</v>
-      </c>
-      <c r="O9" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>122</v>
-      </c>
-      <c r="L10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" t="s">
-        <v>123</v>
-      </c>
-      <c r="N10" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="H11" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K11" t="s">
-        <v>134</v>
-      </c>
-      <c r="L11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" t="s">
-        <v>135</v>
-      </c>
-      <c r="N11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="G12" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="J12" t="s">
-        <v>146</v>
+        <v>53</v>
       </c>
       <c r="K12" t="s">
-        <v>147</v>
-      </c>
-      <c r="L12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M12" t="s">
-        <v>69</v>
-      </c>
-      <c r="N12" t="s">
-        <v>70</v>
-      </c>
-      <c r="O12" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="H13" t="s">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="J13" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>158</v>
-      </c>
-      <c r="L13" t="s">
-        <v>82</v>
-      </c>
-      <c r="M13" t="s">
-        <v>83</v>
-      </c>
-      <c r="N13" t="s">
-        <v>29</v>
-      </c>
-      <c r="O13" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="F14" t="s">
-        <v>165</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="H14" t="s">
-        <v>167</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K14" t="s">
-        <v>169</v>
-      </c>
-      <c r="L14" t="s">
-        <v>95</v>
-      </c>
-      <c r="M14" t="s">
-        <v>96</v>
-      </c>
-      <c r="N14" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="F15" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="G15" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="H15" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="J15" t="s">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s">
-        <v>181</v>
-      </c>
-      <c r="L15" t="s">
-        <v>109</v>
-      </c>
-      <c r="M15" t="s">
-        <v>182</v>
-      </c>
-      <c r="N15" t="s">
-        <v>111</v>
-      </c>
-      <c r="O15" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="F16" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>190</v>
+        <v>136</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="I16" t="s">
-        <v>192</v>
+        <v>33</v>
       </c>
       <c r="J16" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>193</v>
-      </c>
-      <c r="L16" t="s">
-        <v>41</v>
-      </c>
-      <c r="M16" t="s">
-        <v>42</v>
-      </c>
-      <c r="N16" t="s">
-        <v>29</v>
-      </c>
-      <c r="O16" t="s">
-        <v>194</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>198</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="F17" t="s">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="H17" t="s">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>203</v>
+        <v>42</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>123</v>
-      </c>
-      <c r="L17" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" t="s">
-        <v>55</v>
-      </c>
-      <c r="N17" t="s">
-        <v>29</v>
-      </c>
-      <c r="O17" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>147</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
-        <v>208</v>
+        <v>149</v>
       </c>
       <c r="F18" t="s">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="G18" t="s">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="H18" t="s">
-        <v>210</v>
+        <v>51</v>
       </c>
       <c r="I18" t="s">
-        <v>211</v>
+        <v>52</v>
       </c>
       <c r="J18" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="K18" t="s">
-        <v>213</v>
-      </c>
-      <c r="L18" t="s">
-        <v>68</v>
-      </c>
-      <c r="M18" t="s">
-        <v>69</v>
-      </c>
-      <c r="N18" t="s">
-        <v>214</v>
-      </c>
-      <c r="O18" t="s">
-        <v>215</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>216</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
-        <v>217</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="E19" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="F19" t="s">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="H19" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="I19" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="J19" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K19" t="s">
-        <v>223</v>
-      </c>
-      <c r="L19" t="s">
-        <v>82</v>
-      </c>
-      <c r="M19" t="s">
-        <v>83</v>
-      </c>
-      <c r="N19" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s">
-        <v>226</v>
+        <v>162</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="D20" t="s">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="E20" t="s">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>230</v>
+        <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>231</v>
+        <v>166</v>
       </c>
       <c r="H20" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="I20" t="s">
-        <v>233</v>
+        <v>71</v>
       </c>
       <c r="J20" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>234</v>
-      </c>
-      <c r="L20" t="s">
-        <v>95</v>
-      </c>
-      <c r="M20" t="s">
-        <v>96</v>
-      </c>
-      <c r="N20" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" t="s">
-        <v>235</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>236</v>
+        <v>168</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>169</v>
       </c>
       <c r="C21" t="s">
-        <v>238</v>
+        <v>170</v>
       </c>
       <c r="D21" t="s">
-        <v>239</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>240</v>
+        <v>172</v>
       </c>
       <c r="F21" t="s">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="G21" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="H21" t="s">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s">
-        <v>69</v>
-      </c>
-      <c r="L21" t="s">
-        <v>109</v>
-      </c>
-      <c r="M21" t="s">
-        <v>110</v>
-      </c>
-      <c r="N21" t="s">
-        <v>111</v>
-      </c>
-      <c r="O21" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/NUMEX_pre_RStudio/models_iWUE.xlsx
+++ b/NUMEX_pre_RStudio/models_iWUE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -92,22 +92,22 @@
     <t xml:space="preserve">iWUE | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">25.624*** (SE = 4.760, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.546* (SE = 6.899, p = 0.043)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.507 (SE = 7.336, p = 0.636)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-20.319+ (SE = 10.694, p = 0.067)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.789 (SE = , p = )</t>
+    <t xml:space="preserve">25.62*** (SE = 4.76, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.55* (SE = 6.90, p = 0.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51 (SE = 7.34, p = 0.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.32+ (SE = 10.69, p = 0.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.79 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">36</t>
@@ -122,424 +122,367 @@
     <t xml:space="preserve">iWUE | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">36.976*** (SE = 5.794, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.390 (SE = 11.588, p = 0.261)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.654 (SE = 7.665, p = 0.255)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.726 (SE = 13.588, p = 0.903)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.035 (SE = , p = )</t>
+    <t xml:space="preserve">36.66*** (SE = 4.95, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.14+ (SE = 5.71, p = 0.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.20 (SE = 5.97, p = 0.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.5</t>
+    <t xml:space="preserve">0.379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">87.624*** (SE = 5.465, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036 (SE = 6.100, p = 0.995)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.081 (SE = 5.507, p = 0.206)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.022 (SE = 8.734, p = 0.648)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.244 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.106 (SE = , p = )</t>
+    <t xml:space="preserve">86.73*** (SE = 5.09, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02 (SE = 4.29, p = 0.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.48 (SE = 4.22, p = 0.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.96 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">45</t>
   </si>
   <si>
-    <t xml:space="preserve">0.039</t>
+    <t xml:space="preserve">0.036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.24*** (SE = 2.70, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64 (SE = 3.35, p = 0.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86 (SE = 3.34, p = 0.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.72 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">383.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.01*** (SE = 8.13, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.02 (SE = 9.47, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95 (SE = 9.39, p = 0.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.82 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.07*** (SE = 4.51, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.33 (SE = 4.94, p = 0.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.35 (SE = 4.91, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-31.40*** (SE = 0.26, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.03 (SE = 0.32, p = 0.93)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.07 (SE = 0.33, p = 0.84)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-30.66*** (SE = 0.40, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.07+ (SE = 0.47, p = 0.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83 (SE = 0.49, p = 0.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-26.59*** (SE = 0.42, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17 (SE = 0.35, p = 0.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.45 (SE = 0.35, p = 0.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-27.69*** (SE = 0.22, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30 (SE = 0.28, p = 0.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23 (SE = 0.27, p = 0.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-27.28*** (SE = 0.67, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32 (SE = 0.78, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33 (SE = 0.77, p = 0.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-27.68*** (SE = 0.37, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.44 (SE = 0.40, p = 0.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.68 (SE = 0.40, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ci | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.06* (SE = 0.03, p = 0.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.03, p = 0.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08+ (SE = 0.04, p = 0.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-68.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ci | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05+ (SE = 0.02, p = 0.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.04 (SE = 0.02, p = 0.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ci | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.02, p = 0.65)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 (SE = 0.02, p = 0.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.240</t>
   </si>
   <si>
-    <t xml:space="preserve">358.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.017*** (SE = 3.032, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.687 (SE = 4.794, p = 0.170)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.608 (SE = 4.548, p = 0.224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.984 (SE = 6.714, p = 0.378)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.743 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">379.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.754*** (SE = 9.142, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.492 (SE = 12.379, p = 0.664)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.891 (SE = 11.970, p = 0.630)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.202 (SE = 18.768, p = 0.217)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.443 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.573*** (SE = 4.962, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.231 (SE = 6.485, p = 0.526)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.506 (SE = 6.217, p = 0.251)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.086 (SE = 10.545, p = 0.775)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.322 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-31.553*** (SE = 0.289, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282 (SE = 0.419, p = 0.506)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285 (SE = 0.446, p = 0.527)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.750 (SE = 0.650, p = 0.258)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-30.630*** (SE = 0.472, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.170 (SE = 0.945, p = 0.262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788 (SE = 0.625, p = 0.254)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138 (SE = 1.108, p = 0.905)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-26.513*** (SE = 0.451, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006 (SE = 0.502, p = 0.991)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.581 (SE = 0.453, p = 0.207)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332 (SE = 0.719, p = 0.647)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.161 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-27.794*** (SE = 0.250, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551 (SE = 0.395, p = 0.170)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457 (SE = 0.374, p = 0.228)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.486 (SE = 0.553, p = 0.384)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-26.806*** (SE = 0.750, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453 (SE = 1.016, p = 0.662)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.483 (SE = 0.982, p = 0.630)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.986 (SE = 1.540, p = 0.217)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.677 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-27.724*** (SE = 0.406, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.346 (SE = 0.531, p = 0.527)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.613 (SE = 0.509, p = 0.251)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.253 (SE = 0.863, p = 0.775)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ci | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903*** (SE = 0.018, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.055* (SE = 0.026, p = 0.043)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.013 (SE = 0.028, p = 0.636)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.077+ (SE = 0.041, p = 0.067)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.060 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-68.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ci | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860*** (SE = 0.022, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.055 (SE = 0.044, p = 0.261)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.037 (SE = 0.029, p = 0.255)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.007 (SE = 0.052, p = 0.903)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.038 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-13.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ci | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666*** (SE = 0.021, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000 (SE = 0.023, p = 0.997)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.027 (SE = 0.021, p = 0.206)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.015 (SE = 0.033, p = 0.646)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.028 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.054 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-97.7</t>
+    <t xml:space="preserve">-104.5</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">0.725*** (SE = 0.012, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.025 (SE = 0.018, p = 0.171)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.022 (SE = 0.017, p = 0.219)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.023 (SE = 0.026, p = 0.373)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.045 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-133.3</t>
+    <t xml:space="preserve">0.72*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-140.0</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682*** (SE = 0.035, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.021 (SE = 0.047, p = 0.664)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022 (SE = 0.045, p = 0.630)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.092 (SE = 0.071, p = 0.217)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.078 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-20.2</t>
+    <t xml:space="preserve">0.70*** (SE = 0.03, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.06 (SE = 0.04, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.02 (SE = 0.04, p = 0.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-24.0</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724*** (SE = 0.019, p = &lt;0.001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016 (SE = 0.025, p = 0.526)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.029 (SE = 0.024, p = 0.251)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012 (SE = 0.040, p = 0.775)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.013 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.039 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-32.7</t>
+    <t xml:space="preserve">0.72*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 (SE = 0.02, p = 0.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = 0.02, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-39.2</t>
   </si>
 </sst>
 </file>
@@ -1042,398 +985,398 @@
         <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
       </c>
       <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
         <v>40</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>41</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
         <v>42</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>49</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>50</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>51</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>52</v>
-      </c>
-      <c r="J6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
         <v>55</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>56</v>
       </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
       </c>
       <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
         <v>60</v>
-      </c>
-      <c r="H7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
         <v>64</v>
       </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J8" t="s">
         <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
         <v>73</v>
       </c>
-      <c r="B9" t="s">
+      <c r="G9" t="s">
         <v>74</v>
       </c>
-      <c r="C9" t="s">
+      <c r="H9" t="s">
         <v>75</v>
       </c>
-      <c r="D9" t="s">
+      <c r="I9" t="s">
         <v>76</v>
       </c>
-      <c r="E9" t="s">
+      <c r="J9" t="s">
         <v>77</v>
       </c>
-      <c r="F9" t="s">
+      <c r="K9" t="s">
         <v>78</v>
-      </c>
-      <c r="G9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s">
         <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J10" t="s">
         <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
         <v>41</v>
       </c>
-      <c r="I11" t="s">
-        <v>98</v>
-      </c>
       <c r="J11" t="s">
         <v>24</v>
       </c>
       <c r="K11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="K12" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
         <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="J13" t="s">
         <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J14" t="s">
         <v>24</v>
       </c>
       <c r="K14" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H15" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="J15" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
@@ -1445,182 +1388,182 @@
         <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E17" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="H17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" t="s">
         <v>41</v>
       </c>
-      <c r="I17" t="s">
-        <v>42</v>
-      </c>
       <c r="J17" t="s">
         <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>149</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="G18" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="H18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J18" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="K18" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
         <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="H19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J19" t="s">
         <v>24</v>
       </c>
       <c r="K19" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D20" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
         <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J20" t="s">
         <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="H21" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J21" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/NUMEX_pre_RStudio/models_iWUE.xlsx
+++ b/NUMEX_pre_RStudio/models_iWUE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -92,31 +92,31 @@
     <t xml:space="preserve">iWUE | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">25.62*** (SE = 4.76, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.55* (SE = 6.90, p = 0.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51 (SE = 7.34, p = 0.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-20.32+ (SE = 10.69, p = 0.07)</t>
+    <t xml:space="preserve">25.74*** (SE = 3.81, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17 (SE = 5.38, p = 0.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39 (SE = 5.55, p = 0.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.97* (SE = 8.19, p = 0.04)</t>
   </si>
   <si>
     <t xml:space="preserve">0.00 (SE = , p = )</t>
   </si>
   <si>
-    <t xml:space="preserve">15.79 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.1</t>
+    <t xml:space="preserve">11.42 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.1</t>
   </si>
   <si>
     <t xml:space="preserve">iWUE | 1000 | Clarisia</t>
@@ -146,205 +146,220 @@
     <t xml:space="preserve">iWUE | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">86.73*** (SE = 5.09, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02 (SE = 4.29, p = 0.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.48 (SE = 4.22, p = 0.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.96 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
+    <t xml:space="preserve">87.36*** (SE = 4.72, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36 (SE = 4.20, p = 0.93)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.63 (SE = 4.15, p = 0.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.36 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.55*** (SE = 2.71, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95 (SE = 3.34, p = 0.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18 (SE = 3.33, p = 0.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.55 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.56*** (SE = 8.11, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.07 (SE = 9.37, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61 (SE = 9.46, p = 0.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.77 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.07*** (SE = 4.51, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.33 (SE = 4.94, p = 0.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.35 (SE = 4.91, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-31.54*** (SE = 0.31, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58 (SE = 0.44, p = 0.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28 (SE = 0.45, p = 0.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.46* (SE = 0.67, p = 0.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-30.66*** (SE = 0.40, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.07+ (SE = 0.47, p = 0.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83 (SE = 0.49, p = 0.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-26.53*** (SE = 0.39, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = 0.35, p = 0.93)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.30 (SE = 0.34, p = 0.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d13C | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-27.67*** (SE = 0.22, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25 (SE = 0.27, p = 0.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18 (SE = 0.27, p = 0.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.24*** (SE = 2.70, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64 (SE = 3.35, p = 0.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86 (SE = 3.34, p = 0.40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.72 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">383.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.01*** (SE = 8.13, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.02 (SE = 9.47, p = 0.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95 (SE = 9.39, p = 0.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.82 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iWUE | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.07*** (SE = 4.51, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.33 (SE = 4.94, p = 0.30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.35 (SE = 4.91, p = 0.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-31.40*** (SE = 0.26, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03 (SE = 0.32, p = 0.93)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.07 (SE = 0.33, p = 0.84)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-30.66*** (SE = 0.40, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.07+ (SE = 0.47, p = 0.06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83 (SE = 0.49, p = 0.13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-26.59*** (SE = 0.42, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17 (SE = 0.35, p = 0.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.45 (SE = 0.35, p = 0.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d13C | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-27.69*** (SE = 0.22, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30 (SE = 0.28, p = 0.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23 (SE = 0.27, p = 0.40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.9</t>
+    <t xml:space="preserve">145.0</t>
   </si>
   <si>
     <t xml:space="preserve">d13C | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">-27.28*** (SE = 0.67, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32 (SE = 0.78, p = 0.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33 (SE = 0.77, p = 0.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71 (SE = , p = )</t>
+    <t xml:space="preserve">-27.31*** (SE = 0.67, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32 (SE = 0.77, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30 (SE = 0.78, p = 0.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129</t>
   </si>
   <si>
     <t xml:space="preserve">86.6</t>
@@ -374,22 +389,22 @@
     <t xml:space="preserve">Ci | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90*** (SE = 0.02, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.06* (SE = 0.03, p = 0.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01 (SE = 0.03, p = 0.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08+ (SE = 0.04, p = 0.07)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-68.5</t>
+    <t xml:space="preserve">0.90*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.03 (SE = 0.02, p = 0.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.02, p = 0.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07* (SE = 0.03, p = 0.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-76.0</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 1000 | Clarisia</t>
@@ -404,9 +419,6 @@
     <t xml:space="preserve">-0.04 (SE = 0.02, p = 0.13)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.04 (SE = , p = )</t>
-  </si>
-  <si>
     <t xml:space="preserve">-19.8</t>
   </si>
   <si>
@@ -416,22 +428,22 @@
     <t xml:space="preserve">0.67*** (SE = 0.02, p = &lt;0.01)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.01 (SE = 0.02, p = 0.65)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02 (SE = 0.02, p = 0.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03 (SE = , p = )</t>
+    <t xml:space="preserve">-0.00 (SE = 0.02, p = 0.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = 0.02, p = 0.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.05 (SE = , p = )</t>
   </si>
   <si>
-    <t xml:space="preserve">0.240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-104.5</t>
+    <t xml:space="preserve">0.202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-99.5</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 2000 | Myrcia</t>
@@ -440,31 +452,31 @@
     <t xml:space="preserve">0.72*** (SE = 0.01, p = &lt;0.01)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.29)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.39)</t>
   </si>
   <si>
-    <t xml:space="preserve">-140.0</t>
+    <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-137.7</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">0.70*** (SE = 0.03, p = &lt;0.01)</t>
+    <t xml:space="preserve">0.71*** (SE = 0.03, p = &lt;0.01)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.06 (SE = 0.04, p = 0.11)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.02 (SE = 0.04, p = 0.68)</t>
+    <t xml:space="preserve">-0.01 (SE = 0.04, p = 0.71)</t>
   </si>
   <si>
     <t xml:space="preserve">0.08 (SE = , p = )</t>
   </si>
   <si>
-    <t xml:space="preserve">-24.0</t>
+    <t xml:space="preserve">-24.1</t>
   </si>
   <si>
     <t xml:space="preserve">Ci | 3000 | Weinmannia</t>
@@ -1058,36 +1070,36 @@
         <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
@@ -1096,103 +1108,103 @@
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
         <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="F10" t="s">
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s">
         <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
         <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>24</v>
@@ -1201,7 +1213,7 @@
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
         <v>40</v>
@@ -1213,30 +1225,30 @@
         <v>24</v>
       </c>
       <c r="K11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H12" t="s">
         <v>49</v>
@@ -1245,59 +1257,59 @@
         <v>50</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="G13" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>24</v>
@@ -1306,77 +1318,77 @@
         <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="J14" t="s">
         <v>24</v>
       </c>
       <c r="K14" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
         <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
@@ -1388,21 +1400,21 @@
         <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
         <v>24</v>
@@ -1411,7 +1423,7 @@
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H17" t="s">
         <v>40</v>
@@ -1423,30 +1435,30 @@
         <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
         <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G18" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H18" t="s">
         <v>49</v>
@@ -1455,24 +1467,24 @@
         <v>50</v>
       </c>
       <c r="J18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K18" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E19" t="s">
         <v>24</v>
@@ -1481,33 +1493,33 @@
         <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J19" t="s">
         <v>24</v>
       </c>
       <c r="K19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E20" t="s">
         <v>24</v>
@@ -1516,54 +1528,54 @@
         <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J20" t="s">
         <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E21" t="s">
         <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
